--- a/matched_objects.xlsx
+++ b/matched_objects.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:O185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,20 +468,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>created_at_y</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>created_at_r</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>address_y</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>address_r</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>price_y</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>price_r</t>
         </is>
@@ -511,20 +525,26 @@
           <t>129</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="n">
+        <v>46208.4886574074</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>46226.43612268518</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 129</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Минск, проспект Рокоссовского, 129</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>93500</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>93500</v>
       </c>
     </row>
@@ -556,20 +576,26 @@
           <t>53</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="1" t="n">
+        <v>46281.57810185185</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>46281.57986111111</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 53</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 53</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>99023</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>99022.64999999999</v>
       </c>
     </row>
@@ -609,20 +635,26 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="1" t="n">
+        <v>46281.54740740741</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>46281.5493287037</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Минск Чичурина ул. 2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Минск, улица Чичурина, 2</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>94763</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>94763.25999999999</v>
       </c>
     </row>
@@ -662,20 +694,26 @@
           <t>56</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="1" t="n">
+        <v>46279.16462962963</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>46279.1771875</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Минск Руссиянова ул. 56</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Minsk, вуліца Францыска Скарыны, 51Б</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>102027</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>102027.34</v>
       </c>
     </row>
@@ -707,20 +745,26 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="1" t="n">
+        <v>46281.49518518519</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>46281.50067129629</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Минск Партизанская ул. 6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Минск, Партизанская улица</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>61084</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>61084.33</v>
       </c>
     </row>
@@ -760,20 +804,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="1" t="n">
+        <v>46259.75153935186</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>46259.75462962963</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Минск Калиновского ул. 1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Минск, улица Калиновского, 1</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>77500</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>77500</v>
       </c>
     </row>
@@ -813,16 +863,22 @@
           <t>89</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="1" t="n">
+        <v>46251.44984953704</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>46251.45479166666</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Минск Рафиева ул. 89 1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>87900</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>87900</v>
       </c>
     </row>
@@ -862,16 +918,22 @@
           <t>41</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="1" t="n">
+        <v>46251.41917824074</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>46251.40848379629</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Минск Казинца ул. 41</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>75000</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>75000</v>
       </c>
     </row>
@@ -911,20 +973,26 @@
           <t>55</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="1" t="n">
+        <v>46250.28269675926</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46265.29017361111</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Минск Одоевского ул. 55</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Минск, улица Одоевского, 55</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>75000</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>76900</v>
       </c>
     </row>
@@ -956,20 +1024,26 @@
           <t>141к1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="1" t="n">
+        <v>46281.32046296296</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46281.32291666666</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 141 1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Минск, Независимости просп. 141к1</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>106653</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>106653.24</v>
       </c>
     </row>
@@ -1001,20 +1075,26 @@
           <t>121</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="1" t="n">
+        <v>46281.27987268518</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46178.52479166666</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 39 2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Минск, Плеханова ул. 121</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>97405</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>107640.49</v>
       </c>
     </row>
@@ -1054,20 +1134,26 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="1" t="n">
+        <v>46268.47560185185</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46268.46210648148</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Минск Волгоградская ул. 5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Minsk, Валгаградская вуліца, 5</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>112000</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>112000</v>
       </c>
     </row>
@@ -1099,20 +1185,26 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="1" t="n">
+        <v>46274.54996527778</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46274.79493055555</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 39 1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Бирюзова ул., 13</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>71500</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>84857.69</v>
       </c>
     </row>
@@ -1144,20 +1236,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="1" t="n">
+        <v>46274.54996527778</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>46265.6377199074</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 39 1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Одинцова ул., 77 ,1</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>71500</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>85308.72</v>
       </c>
     </row>
@@ -1189,20 +1287,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="1" t="n">
+        <v>46274.54996527778</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>46265.63770833334</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 39 1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Одинцова ул., 77 ,1</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>71500</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>85308.72</v>
       </c>
     </row>
@@ -1234,20 +1338,26 @@
           <t>158</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="1" t="n">
+        <v>46280.74357638889</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46280.74652777778</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 158</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 158</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>102688</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>102687.71</v>
       </c>
     </row>
@@ -1279,20 +1389,26 @@
           <t>56</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="1" t="n">
+        <v>46280.55918981481</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46280.5659837963</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 56</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Минск, Пушкина просп. 56</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>92452</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>92451.96000000001</v>
       </c>
     </row>
@@ -1332,20 +1448,26 @@
           <t>48</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="1" t="n">
+        <v>46280.55157407407</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46280.55159722222</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Минск Куйбышева ул. 48</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Куйбышева, 48</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>113914</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>113914.02</v>
       </c>
     </row>
@@ -1377,20 +1499,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="1" t="n">
+        <v>46220.51450231481</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>46260.20613425926</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 28 1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Минск, Слободская улица, 15</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>80202</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>85848.25</v>
       </c>
     </row>
@@ -1422,20 +1550,26 @@
           <t>28к1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="1" t="n">
+        <v>46220.51450231481</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>46220.62186342593</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 28 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Минск, Звязда газеты просп. 28к1</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>80202</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>80202.07000000001</v>
       </c>
     </row>
@@ -1467,20 +1601,26 @@
           <t>48</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="1" t="n">
+        <v>46220.51450231481</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>46243.73265046296</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 28 1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Минск, Космонавтов ул. 48</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>80202</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>86838.8</v>
       </c>
     </row>
@@ -1512,20 +1652,26 @@
           <t>170</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="1" t="n">
+        <v>46220.51450231481</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46252.87851851852</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 28 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 170</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>80202</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>89480.28999999999</v>
       </c>
     </row>
@@ -1565,20 +1711,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="1" t="n">
+        <v>46197.49895833333</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>46076.68903935186</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>82500</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>82500</v>
       </c>
     </row>
@@ -1618,20 +1770,26 @@
           <t>109</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="1" t="n">
+        <v>46280.36277777778</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>46280.37549768519</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Минск Рафиева ул. 109</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Минск, улица Рафиева, 109</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>115433</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>115432.87</v>
       </c>
     </row>
@@ -1663,20 +1821,26 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="1" t="n">
+        <v>46268.35498842593</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>46279.89821759259</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Минск Коласа ул. 45 2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Minsk, вуліца Розы Люксембург, 82</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>98065</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>119900</v>
       </c>
     </row>
@@ -1716,20 +1880,26 @@
           <t>31</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="1" t="n">
+        <v>46279.84533564815</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>46279.84890046297</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Минск Чигладзе ул. 31</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Минск, улица Чигладзе, 31</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>83000</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>83000</v>
       </c>
     </row>
@@ -1761,20 +1931,26 @@
           <t>117</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="1" t="n">
+        <v>46279.75134259259</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>46279.72769675926</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Минск Есенина ул.</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Минск, улица Сергея Есенина, 117</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>118000</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>118000</v>
       </c>
     </row>
@@ -1814,20 +1990,26 @@
           <t>37</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="1" t="n">
+        <v>46251.32429398148</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>46251.37377314815</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Минск Космонавтов ул. 37</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Минск, улица Космонавтов, 37</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>100000</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1859,20 +2041,26 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="1" t="n">
+        <v>46279.57478009259</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>46279.57986111111</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Минск Багратиона 2-й пер. 17</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Минск, Багратиона 2-й пер. 17</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>90141</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>90140.66</v>
       </c>
     </row>
@@ -1904,20 +2092,26 @@
           <t>67</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="1" t="n">
+        <v>46168.47175925926</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>46232.56950231481</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Минск Партизанский просп. 67</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Минск, Партизанский просп. 67</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>110000</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>110000</v>
       </c>
     </row>
@@ -1949,20 +2143,26 @@
           <t>51</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="1" t="n">
+        <v>46279.44101851852</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>46279.44791666666</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 51</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Минск, Пушкина просп. 51</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>95027</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>95027.41</v>
       </c>
     </row>
@@ -2002,20 +2202,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="1" t="n">
+        <v>46279.43960648148</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>46280.3315162037</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>79145</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>79145.48</v>
       </c>
     </row>
@@ -2055,16 +2261,22 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="1" t="n">
+        <v>46279.40466435185</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>46279.38171296296</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>Минск Воронянского ул. 25</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
         <v>104691</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>104691.28</v>
       </c>
     </row>
@@ -2104,20 +2316,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="1" t="n">
+        <v>46223.9725462963</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>46088.44923611111</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>86500</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>86500</v>
       </c>
     </row>
@@ -2149,20 +2367,26 @@
           <t>153к2</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="1" t="n">
+        <v>46279.26104166666</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>46279.26737268519</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 153 2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Минск, Независимости просп. 153к2</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>102240</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>102239.65</v>
       </c>
     </row>
@@ -2194,20 +2418,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="1" t="n">
+        <v>46046.29599537037</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>46046.40297453704</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Минск Столетова пер. 15</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Минск, Столетова пер. 15</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>84924</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>84923.73</v>
       </c>
     </row>
@@ -2247,16 +2477,22 @@
           <t>105</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="1" t="n">
+        <v>46217.4812037037</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>46265.45190972222</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Минск Селицкого ул. 105</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
         <v>72000</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>72000</v>
       </c>
     </row>
@@ -2296,16 +2532,22 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="1" t="n">
+        <v>46247.36657407408</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>46266.34243055555</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Минск Пуховичская ул. 17</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
         <v>77594</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>77593.61</v>
       </c>
     </row>
@@ -2345,16 +2587,22 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="1" t="n">
+        <v>46142.31697916667</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>46142.31092592593</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Минск Германовская ул. 15</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
         <v>110500</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>110500</v>
       </c>
     </row>
@@ -2394,20 +2642,26 @@
           <t>84</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="1" t="n">
+        <v>46277.33709490741</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>46277.33899305556</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Минск Шаранговича ул. 84</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Минск, улица Шаранговича, 84</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>99056</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>99055.67</v>
       </c>
     </row>
@@ -2439,20 +2693,26 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="1" t="n">
+        <v>46276.82299768519</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>46270.24653935185</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Минск, Братская ул. 17</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>87238</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>110315</v>
       </c>
     </row>
@@ -2484,20 +2744,26 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="1" t="n">
+        <v>46276.82299768519</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>46272.57327546296</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Минск, улица Игоря Лученка, 11</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>87238</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -2529,16 +2795,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="1" t="n">
+        <v>46246.39886574074</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>46281.43928240741</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>Минск Горный пер. 7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
         <v>85188</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>69338.97</v>
       </c>
     </row>
@@ -2570,20 +2842,26 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="1" t="n">
+        <v>46246.39886574074</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>46246.40278935185</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>Минск Горный пер. 7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Минск, Горный пер. 7</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>85188</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>85187.88</v>
       </c>
     </row>
@@ -2615,20 +2893,26 @@
           <t>55</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="1" t="n">
+        <v>46246.39886574074</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>46265.29017361111</v>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>Минск Горный пер. 7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Минск, улица Одоевского, 55</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>85188</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>76900</v>
       </c>
     </row>
@@ -2660,20 +2944,26 @@
           <t>24к4</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="1" t="n">
+        <v>46246.39886574074</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>46255.54513888889</v>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>Минск Горный пер. 7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Минск, Берута ул. 24к4</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>85188</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>64716.37</v>
       </c>
     </row>
@@ -2713,20 +3003,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="1" t="n">
+        <v>46186.59533564815</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>46186.59842592593</v>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>76500</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>76500</v>
       </c>
     </row>
@@ -2766,20 +3062,26 @@
           <t>49</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="1" t="n">
+        <v>46276.46225694445</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>46276.46450231481</v>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>Минск Волоха ул. 49</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Минск, улица Волоха, 49</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>66500</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>66500</v>
       </c>
     </row>
@@ -2811,20 +3113,26 @@
           <t>к1</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="1" t="n">
+        <v>46182.45112268518</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>46183.28061342592</v>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 153 1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Минск, проспект Независимости, 153 к1</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>95754</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>95753.81</v>
       </c>
     </row>
@@ -2864,20 +3172,26 @@
           <t>28</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="1" t="n">
+        <v>46142.53648148148</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>46240.63577546296</v>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>Минск Горовца ул. 28</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Горовца, 28</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>77594</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>77593.61</v>
       </c>
     </row>
@@ -2917,16 +3231,22 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="1" t="n">
+        <v>46246.41182870371</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>46246.57795138889</v>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>Минск Леонида Щемелёва ул. 30</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
         <v>108000</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>108000</v>
       </c>
     </row>
@@ -2966,16 +3286,22 @@
           <t>69</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="1" t="n">
+        <v>46276.4100925926</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>46276.4020949074</v>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>Минск Калиновского ул. 69</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
         <v>88739</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>88738.69</v>
       </c>
     </row>
@@ -3007,20 +3333,26 @@
           <t>23 к</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="1" t="n">
+        <v>46276.35555555556</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>46238.84428240741</v>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Minsk, вуліца Міхаіла Савіцкага</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>88339</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>85980.32000000001</v>
       </c>
     </row>
@@ -3052,20 +3384,26 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="1" t="n">
+        <v>46246.31967592592</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>46261.21005787037</v>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>Минск Партизанский просп. 28 2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Беларусь, г. Минск, Острошицкая ул., 5</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>81985</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>88753.88</v>
       </c>
     </row>
@@ -3097,20 +3435,26 @@
           <t>28к2</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="1" t="n">
+        <v>46246.31967592592</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>46246.43752314815</v>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>Минск Партизанский просп. 28 2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Минск, Партизанский просп. 28к2</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>81985</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>81985.08</v>
       </c>
     </row>
@@ -3142,20 +3486,26 @@
           <t>53</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="1" t="n">
+        <v>46275.7777199074</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>46281.57986111111</v>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>Минск Голодеда проезд 9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 53</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>87499</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>99022.64999999999</v>
       </c>
     </row>
@@ -3195,16 +3545,22 @@
           <t>83</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="1" t="n">
+        <v>46245.5887037037</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>46248.46972222222</v>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>Минск Рафиева ул. 83</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
         <v>82546</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>82546.39</v>
       </c>
     </row>
@@ -3236,20 +3592,26 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="1" t="n">
+        <v>46275.54651620371</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>46275.55209490741</v>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Минск, Пушкина просп. 5</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>104900</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>104900</v>
       </c>
     </row>
@@ -3281,16 +3643,22 @@
           <t>28</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="1" t="n">
+        <v>46275.43314814815</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>46280.61778935185</v>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 130</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
         <v>109622</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>115564.95</v>
       </c>
     </row>
@@ -3322,20 +3690,26 @@
           <t>130</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="1" t="n">
+        <v>46275.43314814815</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>46275.43403935185</v>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 130</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 130</t>
         </is>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>109622</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>109621.61</v>
       </c>
     </row>
@@ -3375,20 +3749,26 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="1" t="n">
+        <v>46212.38091435185</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>46212.38278935185</v>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>Минск Жудро ул. 6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Минск, улица Жудро, 6</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>104174</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>104173.55</v>
       </c>
     </row>
@@ -3420,20 +3800,26 @@
           <t>36</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="1" t="n">
+        <v>46275.33363425926</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>46273.31295138889</v>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 36</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Минск, проспект Пушкина, 36</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>86022</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>86021.59</v>
       </c>
     </row>
@@ -3465,20 +3851,26 @@
           <t>64</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="1" t="n">
+        <v>46275.33363425926</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>46199.20996527778</v>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 36</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Беларусь, г. Минск, Захарова ул., 64</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>86022</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>117711.15</v>
       </c>
     </row>
@@ -3510,20 +3902,26 @@
           <t>7к1</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="1" t="n">
+        <v>46244.56068287037</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>46244.5625</v>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>Минск Голодеда проезд 7 1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Минск, Голодеда проезд 7к1</t>
         </is>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>94433</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>94433.07000000001</v>
       </c>
     </row>
@@ -3555,20 +3953,26 @@
           <t>34к1</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="1" t="n">
+        <v>46274.51453703704</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>46274.51736111111</v>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>Минск Партизанский просп. 34 1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Минск, Партизанский просп. 34к1</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>94900</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>94900</v>
       </c>
     </row>
@@ -3600,20 +4004,26 @@
           <t>43</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="1" t="n">
+        <v>46244.44618055555</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>46266.51736111111</v>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 30 3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Минск, Тухачевского ул. 43</t>
         </is>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
         <v>81759</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>77593.61</v>
       </c>
     </row>
@@ -3645,20 +4055,26 @@
           <t>к3</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="1" t="n">
+        <v>46244.44618055555</v>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>46244.44918981481</v>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 30 3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Минск, Логойский тракт, 30 к3</t>
         </is>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>81759</v>
       </c>
-      <c r="M68" t="n">
+      <c r="O68" t="n">
         <v>81758.89999999999</v>
       </c>
     </row>
@@ -3690,20 +4106,26 @@
           <t>34</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="1" t="n">
+        <v>46274.41511574074</v>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>46239.21033564815</v>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 10 4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Беларусь, г. Минск, Якубовского ул., 34</t>
         </is>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>84000</v>
       </c>
-      <c r="M69" t="n">
+      <c r="O69" t="n">
         <v>73631.38</v>
       </c>
     </row>
@@ -3735,20 +4157,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="1" t="n">
+        <v>46274.41511574074</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>46274.41512731482</v>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 10 4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Звязда газеты просп., 10 ,4</t>
         </is>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>84000</v>
       </c>
-      <c r="M70" t="n">
+      <c r="O70" t="n">
         <v>84000</v>
       </c>
     </row>
@@ -3780,20 +4208,26 @@
           <t>13/3</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="1" t="n">
+        <v>46274.41511574074</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>46182.65351851852</v>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 10 4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Minsk, вуліца Русіянава, 13 к2</t>
         </is>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
         <v>84000</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>73000</v>
       </c>
     </row>
@@ -3825,20 +4259,26 @@
           <t>147</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="1" t="n">
+        <v>46251.81151620371</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>46251.82039351852</v>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 147</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Минск, проспект Рокоссовского, 147</t>
         </is>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>99056</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>99055.67</v>
       </c>
     </row>
@@ -3870,20 +4310,26 @@
           <t>к2</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="1" t="n">
+        <v>46273.7706712963</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>46274.73065972222</v>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 32 2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Минск, Логойский тракт, 32 к2</t>
         </is>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>90966</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>96084</v>
       </c>
     </row>
@@ -3923,20 +4369,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="1" t="n">
+        <v>46273.72288194444</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>46273.73136574074</v>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова</t>
         </is>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>63065</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>63065.44</v>
       </c>
     </row>
@@ -3968,20 +4420,26 @@
           <t>40к1</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="1" t="n">
+        <v>46273.61248842593</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>46274.30903935185</v>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>Минск Любимова просп. 40 1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Минск, Любимова просп. 40к1</t>
         </is>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>106683</v>
       </c>
-      <c r="M75" t="n">
+      <c r="O75" t="n">
         <v>106682.96</v>
       </c>
     </row>
@@ -4013,20 +4471,26 @@
           <t>27</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="1" t="n">
+        <v>46183.6122800926</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>46183.71554398148</v>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 27</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Минск, Логойский тракт 27</t>
         </is>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
         <v>107310</v>
       </c>
-      <c r="M76" t="n">
+      <c r="O76" t="n">
         <v>107310.31</v>
       </c>
     </row>
@@ -4058,20 +4522,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="1" t="n">
+        <v>46176.39760416667</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>46176.55236111111</v>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>Минск Коласа пер. 4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Минск, Коласа пер. 4</t>
         </is>
       </c>
-      <c r="L77" t="n">
+      <c r="N77" t="n">
         <v>114280</v>
       </c>
-      <c r="M77" t="n">
+      <c r="O77" t="n">
         <v>114279.54</v>
       </c>
     </row>
@@ -4103,20 +4573,26 @@
           <t>57</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="1" t="n">
+        <v>46273.30802083333</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>46273.30903935185</v>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 57</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 57</t>
         </is>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>106619</v>
       </c>
-      <c r="M78" t="n">
+      <c r="O78" t="n">
         <v>106618.9</v>
       </c>
     </row>
@@ -4156,20 +4632,26 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="1" t="n">
+        <v>46272.97430555556</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>46273.53978009259</v>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>Минск Игоря Лученка ул. 9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Минск, улица Игоря Лученка, 9</t>
         </is>
       </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
         <v>96000</v>
       </c>
-      <c r="M79" t="n">
+      <c r="O79" t="n">
         <v>96000</v>
       </c>
     </row>
@@ -4201,20 +4683,26 @@
           <t>4к4</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="1" t="n">
+        <v>46272.62136574074</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>46272.6284837963</v>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 4 4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 4к4</t>
         </is>
       </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
         <v>78914</v>
       </c>
-      <c r="M80" t="n">
+      <c r="O80" t="n">
         <v>78914.35000000001</v>
       </c>
     </row>
@@ -4254,20 +4742,26 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="1" t="n">
+        <v>46272.60731481481</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>46177.30440972222</v>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>Минск Кульман ул. 13</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Минск, улица Кульман, 13</t>
         </is>
       </c>
-      <c r="L81" t="n">
+      <c r="N81" t="n">
         <v>107740</v>
       </c>
-      <c r="M81" t="n">
+      <c r="O81" t="n">
         <v>107739.55</v>
       </c>
     </row>
@@ -4299,20 +4793,26 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="1" t="n">
+        <v>46272.30520833333</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>46272.30903935185</v>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>Минск Уральский пер. 7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Минск, Уральский пер. 7</t>
         </is>
       </c>
-      <c r="L82" t="n">
+      <c r="N82" t="n">
         <v>106287</v>
       </c>
-      <c r="M82" t="n">
+      <c r="O82" t="n">
         <v>106286.73</v>
       </c>
     </row>
@@ -4352,20 +4852,26 @@
           <t>19</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="1" t="n">
+        <v>46241.7108912037</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>46241.71923611111</v>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>Минск Бирюзова ул. 19</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>Минск, улица Бирюзова, 19</t>
         </is>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
         <v>88219</v>
       </c>
-      <c r="M83" t="n">
+      <c r="O83" t="n">
         <v>88218.98</v>
       </c>
     </row>
@@ -4405,16 +4911,22 @@
           <t>37</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="1" t="n">
+        <v>46211.39453703703</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>46211.4555787037</v>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>Минск Одоевского ул. 37</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="n">
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
         <v>119000</v>
       </c>
-      <c r="M84" t="n">
+      <c r="O84" t="n">
         <v>119000</v>
       </c>
     </row>
@@ -4446,20 +4958,26 @@
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="1" t="n">
+        <v>46240.51386574074</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>46260.79651620371</v>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>Минск Кунцевщина ул. 36</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Minsk, Шафарнянская вуліца, 2</t>
         </is>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>89150</v>
       </c>
-      <c r="M85" t="n">
+      <c r="O85" t="n">
         <v>88888</v>
       </c>
     </row>
@@ -4499,16 +5017,22 @@
           <t>122</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="1" t="n">
+        <v>46240.42582175926</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>46266.56631944444</v>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>Минск Казинца ул. 122</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="n">
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
         <v>109000</v>
       </c>
-      <c r="M86" t="n">
+      <c r="O86" t="n">
         <v>109000</v>
       </c>
     </row>
@@ -4548,20 +5072,26 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="1" t="n">
+        <v>46210.37053240741</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>46210.37660879629</v>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>Минск Пирогова ул. 6</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Минск, улица Пирогова, 6</t>
         </is>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>119857</v>
       </c>
-      <c r="M87" t="n">
+      <c r="O87" t="n">
         <v>119857.36</v>
       </c>
     </row>
@@ -4593,20 +5123,26 @@
           <t>к1</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="1" t="n">
+        <v>46149.66276620371</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>46149.45806712963</v>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 14 1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Минск, проспект Газеты Звязда, 14 к1</t>
         </is>
       </c>
-      <c r="L88" t="n">
+      <c r="N88" t="n">
         <v>85500</v>
       </c>
-      <c r="M88" t="n">
+      <c r="O88" t="n">
         <v>85500</v>
       </c>
     </row>
@@ -4638,20 +5174,26 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="1" t="n">
+        <v>46149.66276620371</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>46268.67361111111</v>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 14 1</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>Минск, Голодеда ул. 25</t>
         </is>
       </c>
-      <c r="L89" t="n">
+      <c r="N89" t="n">
         <v>85500</v>
       </c>
-      <c r="M89" t="n">
+      <c r="O89" t="n">
         <v>79660</v>
       </c>
     </row>
@@ -4683,20 +5225,26 @@
           <t>95</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="1" t="n">
+        <v>46149.66276620371</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>46274.58681712963</v>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 14 1</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>Минск, Слободская ул. 95</t>
         </is>
       </c>
-      <c r="L90" t="n">
+      <c r="N90" t="n">
         <v>85500</v>
       </c>
-      <c r="M90" t="n">
+      <c r="O90" t="n">
         <v>78584.16</v>
       </c>
     </row>
@@ -4728,20 +5276,26 @@
           <t>18</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="1" t="n">
+        <v>46149.66276620371</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>46255.20913194444</v>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 14 1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>Беларусь, г. Минск, Руссиянова ул., 18</t>
         </is>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>85500</v>
       </c>
-      <c r="M91" t="n">
+      <c r="O91" t="n">
         <v>98263.22</v>
       </c>
     </row>
@@ -4773,20 +5327,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="1" t="n">
+        <v>46239.61550925926</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>46239.62862268519</v>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>Минск Игуменский тракт 45</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Минск, Игуменский тракт, 45</t>
         </is>
       </c>
-      <c r="L92" t="n">
+      <c r="N92" t="n">
         <v>115169</v>
       </c>
-      <c r="M92" t="n">
+      <c r="O92" t="n">
         <v>115168.72</v>
       </c>
     </row>
@@ -4818,20 +5378,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="1" t="n">
+        <v>46268.80193287037</v>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>46268.80902777778</v>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>Минск Партизанский просп. 22</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Минск, Партизанский просп. 22</t>
         </is>
       </c>
-      <c r="L93" t="n">
+      <c r="N93" t="n">
         <v>93218</v>
       </c>
-      <c r="M93" t="n">
+      <c r="O93" t="n">
         <v>93217.99000000001</v>
       </c>
     </row>
@@ -4871,20 +5437,26 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="1" t="n">
+        <v>46222.83648148148</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>46222.85458333333</v>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>Минск Игоря Лученка ул. 7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Минск, улица Игоря Лученка, 7</t>
         </is>
       </c>
-      <c r="L94" t="n">
+      <c r="N94" t="n">
         <v>107000</v>
       </c>
-      <c r="M94" t="n">
+      <c r="O94" t="n">
         <v>107000</v>
       </c>
     </row>
@@ -4916,20 +5488,26 @@
           <t>26</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="1" t="n">
+        <v>46268.50037037037</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>46268.50347222222</v>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 26</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Минск, Пушкина просп. 26</t>
         </is>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>115000</v>
       </c>
-      <c r="M95" t="n">
+      <c r="O95" t="n">
         <v>115000</v>
       </c>
     </row>
@@ -4961,20 +5539,26 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="1" t="n">
+        <v>46238.48640046296</v>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>46269.5341550926</v>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>Минск Правда газеты просп. 30</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Правда газеты просп., 30</t>
         </is>
       </c>
-      <c r="L96" t="n">
+      <c r="N96" t="n">
         <v>94664</v>
       </c>
-      <c r="M96" t="n">
+      <c r="O96" t="n">
         <v>94664.2</v>
       </c>
     </row>
@@ -5014,16 +5598,22 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="1" t="n">
+        <v>46268.47489583334</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>46268.46894675926</v>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>Минск Ольшевского ул. 4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="n">
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="n">
         <v>89150</v>
       </c>
-      <c r="M97" t="n">
+      <c r="O97" t="n">
         <v>89150.10000000001</v>
       </c>
     </row>
@@ -5055,20 +5645,26 @@
           <t>36</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="1" t="n">
+        <v>46268.44217592593</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>46268.44791666666</v>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>Минск Игуменский тракт 36</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Минск, Игуменский тракт 36</t>
         </is>
       </c>
-      <c r="L98" t="n">
+      <c r="N98" t="n">
         <v>105990</v>
       </c>
-      <c r="M98" t="n">
+      <c r="O98" t="n">
         <v>105989.57</v>
       </c>
     </row>
@@ -5100,20 +5696,26 @@
           <t>85</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="1" t="n">
+        <v>46268.42444444444</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>46269.20965277778</v>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 85</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>Беларусь, г. Минск, Пушкина пр., 85</t>
         </is>
       </c>
-      <c r="L99" t="n">
+      <c r="N99" t="n">
         <v>119659</v>
       </c>
-      <c r="M99" t="n">
+      <c r="O99" t="n">
         <v>119659.25</v>
       </c>
     </row>
@@ -5153,20 +5755,26 @@
           <t>26</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="1" t="n">
+        <v>46238.37222222222</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>46238.37224537037</v>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>Минск Леонида Щемелёва ул. 26</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Леонида Щемелёва, 26</t>
         </is>
       </c>
-      <c r="L100" t="n">
+      <c r="N100" t="n">
         <v>78584</v>
       </c>
-      <c r="M100" t="n">
+      <c r="O100" t="n">
         <v>78584.16</v>
       </c>
     </row>
@@ -5198,20 +5806,26 @@
           <t>90</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="1" t="n">
+        <v>46232.29756944445</v>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>46252.961875</v>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>Минск Дзержинского просп. 90</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>Минск, Дзержинского просп. 90</t>
         </is>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>116556</v>
       </c>
-      <c r="M101" t="n">
+      <c r="O101" t="n">
         <v>116555.5</v>
       </c>
     </row>
@@ -5243,20 +5857,26 @@
           <t>114</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="1" t="n">
+        <v>46148.30716435185</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>46148.42032407408</v>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 114</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 114</t>
         </is>
       </c>
-      <c r="L102" t="n">
+      <c r="N102" t="n">
         <v>117154</v>
       </c>
-      <c r="M102" t="n">
+      <c r="O102" t="n">
         <v>117154.46</v>
       </c>
     </row>
@@ -5288,16 +5908,22 @@
           <t>115</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="1" t="n">
+        <v>46267.66318287037</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>46267.65773148148</v>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 115</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="n">
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="n">
         <v>115000</v>
       </c>
-      <c r="M103" t="n">
+      <c r="O103" t="n">
         <v>115000</v>
       </c>
     </row>
@@ -5337,20 +5963,26 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="1" t="n">
+        <v>46267.55384259259</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>46267.55353009259</v>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>Минск Гамарника ул. 23</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Гамарника, 23</t>
         </is>
       </c>
-      <c r="L104" t="n">
+      <c r="N104" t="n">
         <v>82546</v>
       </c>
-      <c r="M104" t="n">
+      <c r="O104" t="n">
         <v>82546.39</v>
       </c>
     </row>
@@ -5382,20 +6014,26 @@
           <t>21ка</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J105" s="1" t="n">
+        <v>46237.47337962963</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>46237.48959490741</v>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 21 А</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>Минск, Логойский тракт 21кА</t>
         </is>
       </c>
-      <c r="L105" t="n">
+      <c r="N105" t="n">
         <v>111933</v>
       </c>
-      <c r="M105" t="n">
+      <c r="O105" t="n">
         <v>111932.91</v>
       </c>
     </row>
@@ -5435,20 +6073,26 @@
           <t>26</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J106" s="1" t="n">
+        <v>46237.38289351852</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <v>46237.38489583333</v>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>Минск Игоря Лученка ул. 26</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>Минск, улица Игоря Лученка, 26</t>
         </is>
       </c>
-      <c r="L106" t="n">
+      <c r="N106" t="n">
         <v>108631</v>
       </c>
-      <c r="M106" t="n">
+      <c r="O106" t="n">
         <v>108631.05</v>
       </c>
     </row>
@@ -5488,20 +6132,26 @@
           <t>16</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J107" s="1" t="n">
+        <v>46266.65824074074</v>
+      </c>
+      <c r="K107" s="1" t="n">
+        <v>46266.65768518519</v>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t>Минск Жуковского ул. 16</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>Минск, улица Жуковского, 16</t>
         </is>
       </c>
-      <c r="L107" t="n">
+      <c r="N107" t="n">
         <v>89365</v>
       </c>
-      <c r="M107" t="n">
+      <c r="O107" t="n">
         <v>89364.72</v>
       </c>
     </row>
@@ -5541,20 +6191,26 @@
           <t>36</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J108" s="1" t="n">
+        <v>46266.44055555556</v>
+      </c>
+      <c r="K108" s="1" t="n">
+        <v>46266.44060185185</v>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t>Минск Шаранговича ул. 36</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, Шаранговича, 36</t>
         </is>
       </c>
-      <c r="L108" t="n">
+      <c r="N108" t="n">
         <v>115565</v>
       </c>
-      <c r="M108" t="n">
+      <c r="O108" t="n">
         <v>115564.95</v>
       </c>
     </row>
@@ -5594,20 +6250,26 @@
           <t>76</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J109" s="1" t="n">
+        <v>46247.49841435185</v>
+      </c>
+      <c r="K109" s="1" t="n">
+        <v>46247.49445601852</v>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t>Минск Казинца ул. 76</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>Минск, улица Казинца, 76</t>
         </is>
       </c>
-      <c r="L109" t="n">
+      <c r="N109" t="n">
         <v>97405</v>
       </c>
-      <c r="M109" t="n">
+      <c r="O109" t="n">
         <v>97404.74000000001</v>
       </c>
     </row>
@@ -5647,20 +6309,26 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J110" s="1" t="n">
+        <v>46265.69037037037</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>46265.70261574074</v>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t>Минск Бирюзова ул. 5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>Минск, улица Бирюзова, 5</t>
         </is>
       </c>
-      <c r="L110" t="n">
+      <c r="N110" t="n">
         <v>95754</v>
       </c>
-      <c r="M110" t="n">
+      <c r="O110" t="n">
         <v>95753.81</v>
       </c>
     </row>
@@ -5692,20 +6360,26 @@
           <t>79</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111" s="1" t="n">
+        <v>46265.53525462963</v>
+      </c>
+      <c r="K111" s="1" t="n">
+        <v>46265.55306712963</v>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 79</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>Минск, проспект Пушкина, 79</t>
         </is>
       </c>
-      <c r="L111" t="n">
+      <c r="N111" t="n">
         <v>91131</v>
       </c>
-      <c r="M111" t="n">
+      <c r="O111" t="n">
         <v>91131.22</v>
       </c>
     </row>
@@ -5737,16 +6411,22 @@
           <t>42</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J112" s="1" t="n">
+        <v>46074.36236111111</v>
+      </c>
+      <c r="K112" s="1" t="n">
+        <v>46175.64709490741</v>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>Минск Игуменский тракт 42</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="n">
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
         <v>119500</v>
       </c>
-      <c r="M112" t="n">
+      <c r="O112" t="n">
         <v>119500</v>
       </c>
     </row>
@@ -5778,20 +6458,26 @@
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr">
+      <c r="J113" s="1" t="n">
+        <v>46265.4446875</v>
+      </c>
+      <c r="K113" s="1" t="n">
+        <v>46265.44472222222</v>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t>Минск Авангардная ул. 9 А</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Авангардная ул., 9 ,а</t>
         </is>
       </c>
-      <c r="L113" t="n">
+      <c r="N113" t="n">
         <v>85000</v>
       </c>
-      <c r="M113" t="n">
+      <c r="O113" t="n">
         <v>85000</v>
       </c>
     </row>
@@ -5823,20 +6509,26 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J114" s="1" t="n">
+        <v>46265.37341435185</v>
+      </c>
+      <c r="K114" s="1" t="n">
+        <v>46265.37409722222</v>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>Минск Кабушкина пер. 11</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Кабушкина пер., 11</t>
         </is>
       </c>
-      <c r="L114" t="n">
+      <c r="N114" t="n">
         <v>105000</v>
       </c>
-      <c r="M114" t="n">
+      <c r="O114" t="n">
         <v>105000</v>
       </c>
     </row>
@@ -5868,20 +6560,26 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="J115" s="1" t="n">
+        <v>46265.31039351852</v>
+      </c>
+      <c r="K115" s="1" t="n">
+        <v>46270.24653935185</v>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>Минск, Братская ул. 17</t>
         </is>
       </c>
-      <c r="L115" t="n">
+      <c r="N115" t="n">
         <v>87238</v>
       </c>
-      <c r="M115" t="n">
+      <c r="O115" t="n">
         <v>110315</v>
       </c>
     </row>
@@ -5913,20 +6611,26 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J116" s="1" t="n">
+        <v>46265.31039351852</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <v>46272.57327546296</v>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>Минск, улица Игоря Лученка, 11</t>
         </is>
       </c>
-      <c r="L116" t="n">
+      <c r="N116" t="n">
         <v>87238</v>
       </c>
-      <c r="M116" t="n">
+      <c r="O116" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -5950,20 +6654,26 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="1" t="n">
+        <v>46234.45057870371</v>
+      </c>
+      <c r="K117" s="1" t="n">
+        <v>46234.48060185185</v>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>Минск Слободской проезд 14</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>Минск, Слободской проезд</t>
         </is>
       </c>
-      <c r="L117" t="n">
+      <c r="N117" t="n">
         <v>94961</v>
       </c>
-      <c r="M117" t="n">
+      <c r="O117" t="n">
         <v>94961.37</v>
       </c>
     </row>
@@ -6003,20 +6713,26 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="J118" s="1" t="n">
+        <v>46209.57170138889</v>
+      </c>
+      <c r="K118" s="1" t="n">
+        <v>46209.57717592592</v>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t>Минск Павлины Медёлки ул. 7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>Минск, улица Павлины Медёлки, 7</t>
         </is>
       </c>
-      <c r="L118" t="n">
+      <c r="N118" t="n">
         <v>104008</v>
       </c>
-      <c r="M118" t="n">
+      <c r="O118" t="n">
         <v>104008.45</v>
       </c>
     </row>
@@ -6048,20 +6764,26 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="J119" s="1" t="n">
+        <v>46263.60253472222</v>
+      </c>
+      <c r="K119" s="1" t="n">
+        <v>46270.24653935185</v>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>Минск, Братская ул. 17</t>
         </is>
       </c>
-      <c r="L119" t="n">
+      <c r="N119" t="n">
         <v>87238</v>
       </c>
-      <c r="M119" t="n">
+      <c r="O119" t="n">
         <v>110315</v>
       </c>
     </row>
@@ -6093,20 +6815,26 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J120" s="1" t="n">
+        <v>46263.60253472222</v>
+      </c>
+      <c r="K120" s="1" t="n">
+        <v>46272.57327546296</v>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t>Минск Мира просп. 8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>Минск, улица Игоря Лученка, 11</t>
         </is>
       </c>
-      <c r="L120" t="n">
+      <c r="N120" t="n">
         <v>87238</v>
       </c>
-      <c r="M120" t="n">
+      <c r="O120" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -6138,20 +6866,26 @@
           <t>112</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J121" s="1" t="n">
+        <v>46203.56373842592</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <v>46203.60640046297</v>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 112</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>Минск, проспект Рокоссовского, 112</t>
         </is>
       </c>
-      <c r="L121" t="n">
+      <c r="N121" t="n">
         <v>93921</v>
       </c>
-      <c r="M121" t="n">
+      <c r="O121" t="n">
         <v>93921.28</v>
       </c>
     </row>
@@ -6183,20 +6917,26 @@
           <t>к2</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="J122" s="1" t="n">
+        <v>46263.40730324074</v>
+      </c>
+      <c r="K122" s="1" t="n">
+        <v>46263.40962962963</v>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 28 2</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>Минск, Логойский тракт, 28 к2</t>
         </is>
       </c>
-      <c r="L122" t="n">
+      <c r="N122" t="n">
         <v>74622</v>
       </c>
-      <c r="M122" t="n">
+      <c r="O122" t="n">
         <v>74621.94</v>
       </c>
     </row>
@@ -6228,20 +6968,26 @@
           <t>168</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J123" s="1" t="n">
+        <v>45629.35724537037</v>
+      </c>
+      <c r="K123" s="1" t="n">
+        <v>45708.31116898148</v>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 168 1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Независимости просп., 168</t>
         </is>
       </c>
-      <c r="L123" t="n">
+      <c r="N123" t="n">
         <v>114905</v>
       </c>
-      <c r="M123" t="n">
+      <c r="O123" t="n">
         <v>114927.34</v>
       </c>
     </row>
@@ -6273,20 +7019,26 @@
           <t>14к1</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J124" s="1" t="n">
+        <v>46233.33383101852</v>
+      </c>
+      <c r="K124" s="1" t="n">
+        <v>46233.33681712963</v>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t>Минск Звязда газеты просп. 14 1</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>Минск, Звязда газеты просп. 14к1</t>
         </is>
       </c>
-      <c r="L124" t="n">
+      <c r="N124" t="n">
         <v>101367</v>
       </c>
-      <c r="M124" t="n">
+      <c r="O124" t="n">
         <v>101366.97</v>
       </c>
     </row>
@@ -6318,20 +7070,26 @@
           <t>168</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J125" s="1" t="n">
+        <v>45745.63383101852</v>
+      </c>
+      <c r="K125" s="1" t="n">
+        <v>45745.63383101852</v>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 168 2</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Независимости просп., 168</t>
         </is>
       </c>
-      <c r="L125" t="n">
+      <c r="N125" t="n">
         <v>114905</v>
       </c>
-      <c r="M125" t="n">
+      <c r="O125" t="n">
         <v>113159.69</v>
       </c>
     </row>
@@ -6371,20 +7129,26 @@
           <t>83</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="J126" s="1" t="n">
+        <v>46262.60841435185</v>
+      </c>
+      <c r="K126" s="1" t="n">
+        <v>46262.6084837963</v>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t>Минск Калиновского ул. 83</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Калиновского, 83</t>
         </is>
       </c>
-      <c r="L126" t="n">
+      <c r="N126" t="n">
         <v>91626</v>
       </c>
-      <c r="M126" t="n">
+      <c r="O126" t="n">
         <v>91626.49000000001</v>
       </c>
     </row>
@@ -6416,20 +7180,26 @@
           <t>31</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J127" s="1" t="n">
+        <v>46232.44872685185</v>
+      </c>
+      <c r="K127" s="1" t="n">
+        <v>46280.48958333334</v>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 153 1</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>Минск, Кошевого ул. 31</t>
         </is>
       </c>
-      <c r="L127" t="n">
+      <c r="N127" t="n">
         <v>97940</v>
       </c>
-      <c r="M127" t="n">
+      <c r="O127" t="n">
         <v>84857.69</v>
       </c>
     </row>
@@ -6461,20 +7231,26 @@
           <t>153к1</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="1" t="n">
+        <v>46232.44872685185</v>
+      </c>
+      <c r="K128" s="1" t="n">
+        <v>46232.45140046296</v>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 153 1</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t>Минск, Независимости просп. 153к1</t>
         </is>
       </c>
-      <c r="L128" t="n">
+      <c r="N128" t="n">
         <v>97940</v>
       </c>
-      <c r="M128" t="n">
+      <c r="O128" t="n">
         <v>97939.64</v>
       </c>
     </row>
@@ -6506,20 +7282,26 @@
           <t>46к2</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="J129" s="1" t="n">
+        <v>46261.67425925926</v>
+      </c>
+      <c r="K129" s="1" t="n">
+        <v>46261.67709490741</v>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t>Минск Любимова просп. 46 2</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>Минск, Любимова просп. 46к2</t>
         </is>
       </c>
-      <c r="L129" t="n">
+      <c r="N129" t="n">
         <v>81226</v>
       </c>
-      <c r="M129" t="n">
+      <c r="O129" t="n">
         <v>81225.64999999999</v>
       </c>
     </row>
@@ -6551,20 +7333,26 @@
           <t>168к2</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="J130" s="1" t="n">
+        <v>46261.60090277778</v>
+      </c>
+      <c r="K130" s="1" t="n">
+        <v>46261.60765046296</v>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 168 2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>Минск, Независимости просп. 168к2</t>
         </is>
       </c>
-      <c r="L130" t="n">
+      <c r="N130" t="n">
         <v>113254</v>
       </c>
-      <c r="M130" t="n">
+      <c r="O130" t="n">
         <v>113253.65</v>
       </c>
     </row>
@@ -6604,20 +7392,26 @@
           <t>73</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J131" s="1" t="n">
+        <v>46171.52302083333</v>
+      </c>
+      <c r="K131" s="1" t="n">
+        <v>46171.53166666667</v>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t>Минск Виталия Цвирко ул. 73</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t>Минск, улица Виталия Цвирко, 73</t>
         </is>
       </c>
-      <c r="L131" t="n">
+      <c r="N131" t="n">
         <v>104339</v>
       </c>
-      <c r="M131" t="n">
+      <c r="O131" t="n">
         <v>104338.64</v>
       </c>
     </row>
@@ -6657,16 +7451,22 @@
           <t>87</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="1" t="n">
+        <v>46231.41708333333</v>
+      </c>
+      <c r="K132" s="1" t="n">
+        <v>46231.42054398148</v>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t>Минск Одинцова ул. 87</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="n">
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="n">
         <v>93000</v>
       </c>
-      <c r="M132" t="n">
+      <c r="O132" t="n">
         <v>93000</v>
       </c>
     </row>
@@ -6706,20 +7506,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="1" t="n">
+        <v>46120.74285879629</v>
+      </c>
+      <c r="K133" s="1" t="n">
+        <v>46120.74895833333</v>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>Minsk, вуліца Жарэса Алфёрава</t>
         </is>
       </c>
-      <c r="L133" t="n">
+      <c r="N133" t="n">
         <v>52830</v>
       </c>
-      <c r="M133" t="n">
+      <c r="O133" t="n">
         <v>52829.69</v>
       </c>
     </row>
@@ -6751,20 +7557,26 @@
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr">
+      <c r="J134" s="1" t="n">
+        <v>46260.69415509259</v>
+      </c>
+      <c r="K134" s="1" t="n">
+        <v>46260.79651620371</v>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t>Минск Никифорова ул. 25</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t>Minsk, Шафарнянская вуліца, 2</t>
         </is>
       </c>
-      <c r="L134" t="n">
+      <c r="N134" t="n">
         <v>82900</v>
       </c>
-      <c r="M134" t="n">
+      <c r="O134" t="n">
         <v>88888</v>
       </c>
     </row>
@@ -6804,20 +7616,26 @@
           <t>14</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J135" s="1" t="n">
+        <v>46260.6374537037</v>
+      </c>
+      <c r="K135" s="1" t="n">
+        <v>46260.63608796296</v>
+      </c>
+      <c r="L135" t="inlineStr">
         <is>
           <t>Минск Бельского ул. 14</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>Минск, улица Бельского, 14</t>
         </is>
       </c>
-      <c r="L135" t="n">
+      <c r="N135" t="n">
         <v>110000</v>
       </c>
-      <c r="M135" t="n">
+      <c r="O135" t="n">
         <v>110000</v>
       </c>
     </row>
@@ -6849,20 +7667,26 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J136" s="1" t="n">
+        <v>46260.56729166667</v>
+      </c>
+      <c r="K136" s="1" t="n">
+        <v>46260.57291666666</v>
+      </c>
+      <c r="L136" t="inlineStr">
         <is>
           <t>Минск Мира просп. 12</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>Минск, Мира просп. 12</t>
         </is>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>109622</v>
       </c>
-      <c r="M136" t="n">
+      <c r="O136" t="n">
         <v>109621.61</v>
       </c>
     </row>
@@ -6902,20 +7726,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J137" s="1" t="n">
+        <v>46128.50363425926</v>
+      </c>
+      <c r="K137" s="1" t="n">
+        <v>46127.88140046296</v>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>Minsk, вуліца Жарэса Алфёрава</t>
         </is>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>59698</v>
       </c>
-      <c r="M137" t="n">
+      <c r="O137" t="n">
         <v>59697.55</v>
       </c>
     </row>
@@ -6955,16 +7785,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="J138" s="1" t="n">
+        <v>46260.41883101852</v>
+      </c>
+      <c r="K138" s="1" t="n">
+        <v>46260.42399305556</v>
+      </c>
+      <c r="L138" t="inlineStr">
         <is>
           <t>Минск Пржевальского ул. 2</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="n">
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="n">
         <v>99000</v>
       </c>
-      <c r="M138" t="n">
+      <c r="O138" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -7004,20 +7840,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J139" s="1" t="n">
+        <v>46230.31083333334</v>
+      </c>
+      <c r="K139" s="1" t="n">
+        <v>46230.32273148148</v>
+      </c>
+      <c r="L139" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L139" t="n">
+      <c r="N139" t="n">
         <v>85848</v>
       </c>
-      <c r="M139" t="n">
+      <c r="O139" t="n">
         <v>85848.25</v>
       </c>
     </row>
@@ -7057,20 +7899,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J140" s="1" t="n">
+        <v>46260.30924768518</v>
+      </c>
+      <c r="K140" s="1" t="n">
+        <v>46260.41582175926</v>
+      </c>
+      <c r="L140" t="inlineStr">
         <is>
           <t>Минск Николы Теслы ул. 4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>Минск, улица Николы Теслы, 4</t>
         </is>
       </c>
-      <c r="L140" t="n">
+      <c r="N140" t="n">
         <v>103348</v>
       </c>
-      <c r="M140" t="n">
+      <c r="O140" t="n">
         <v>103348.08</v>
       </c>
     </row>
@@ -7102,20 +7950,26 @@
           <t>89</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J141" s="1" t="n">
+        <v>46139.53755787037</v>
+      </c>
+      <c r="K141" s="1" t="n">
+        <v>46139.53756944444</v>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 89</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t>Беларусь, Минск, Рокоссовского просп., 89</t>
         </is>
       </c>
-      <c r="L141" t="n">
+      <c r="N141" t="n">
         <v>93000</v>
       </c>
-      <c r="M141" t="n">
+      <c r="O141" t="n">
         <v>93000</v>
       </c>
     </row>
@@ -7155,20 +8009,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J142" s="1" t="n">
+        <v>46259.42739583334</v>
+      </c>
+      <c r="K142" s="1" t="n">
+        <v>46259.42888888889</v>
+      </c>
+      <c r="L142" t="inlineStr">
         <is>
           <t>Минск Щорса ул. 1</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t>Minsk, вуліца Шчорса, 1</t>
         </is>
       </c>
-      <c r="L142" t="n">
+      <c r="N142" t="n">
         <v>115103</v>
       </c>
-      <c r="M142" t="n">
+      <c r="O142" t="n">
         <v>115102.69</v>
       </c>
     </row>
@@ -7208,20 +8068,26 @@
           <t>11</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="J143" s="1" t="n">
+        <v>46258.321875</v>
+      </c>
+      <c r="K143" s="1" t="n">
+        <v>46258.32921296296</v>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t>Минск Янковского ул. 11</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>Minsk, вуліца Янкоўскага, 11</t>
         </is>
       </c>
-      <c r="L143" t="n">
+      <c r="N143" t="n">
         <v>89810</v>
       </c>
-      <c r="M143" t="n">
+      <c r="O143" t="n">
         <v>89810.47</v>
       </c>
     </row>
@@ -7261,16 +8127,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="J144" s="1" t="n">
+        <v>46258.2865625</v>
+      </c>
+      <c r="K144" s="1" t="n">
+        <v>46258.28133101852</v>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t>Минск Ташкентская ул. 2</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="n">
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="n">
         <v>99700</v>
       </c>
-      <c r="M144" t="n">
+      <c r="O144" t="n">
         <v>99700</v>
       </c>
     </row>
@@ -7310,20 +8182,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="J145" s="1" t="n">
+        <v>46197.64106481482</v>
+      </c>
+      <c r="K145" s="1" t="n">
+        <v>46197.64825231482</v>
+      </c>
+      <c r="L145" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L145" t="n">
+      <c r="N145" t="n">
         <v>58889</v>
       </c>
-      <c r="M145" t="n">
+      <c r="O145" t="n">
         <v>58888.6</v>
       </c>
     </row>
@@ -7363,20 +8241,26 @@
           <t>37</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J146" s="1" t="n">
+        <v>46227.51674768519</v>
+      </c>
+      <c r="K146" s="1" t="n">
+        <v>46227.51934027778</v>
+      </c>
+      <c r="L146" t="inlineStr">
         <is>
           <t>Минск Одинцова ул. 37</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t>Минск, улица Одинцова, 37</t>
         </is>
       </c>
-      <c r="L146" t="n">
+      <c r="N146" t="n">
         <v>104008</v>
       </c>
-      <c r="M146" t="n">
+      <c r="O146" t="n">
         <v>104008.45</v>
       </c>
     </row>
@@ -7416,20 +8300,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="J147" s="1" t="n">
+        <v>46197.4649537037</v>
+      </c>
+      <c r="K147" s="1" t="n">
+        <v>46197.47461805555</v>
+      </c>
+      <c r="L147" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L147" t="n">
+      <c r="N147" t="n">
         <v>80000</v>
       </c>
-      <c r="M147" t="n">
+      <c r="O147" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -7453,20 +8343,26 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr">
+      <c r="J148" s="1" t="n">
+        <v>46227.32280092593</v>
+      </c>
+      <c r="K148" s="1" t="n">
+        <v>46252.96880787037</v>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t>Минск Савицкого ул.</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>Минск, Савицкого ул.</t>
         </is>
       </c>
-      <c r="L148" t="n">
+      <c r="N148" t="n">
         <v>73783</v>
       </c>
-      <c r="M148" t="n">
+      <c r="O148" t="n">
         <v>73782.61</v>
       </c>
     </row>
@@ -7506,20 +8402,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J149" s="1" t="n">
+        <v>46196.94180555556</v>
+      </c>
+      <c r="K149" s="1" t="n">
+        <v>46196.94576388889</v>
+      </c>
+      <c r="L149" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L149" t="n">
+      <c r="N149" t="n">
         <v>58608</v>
       </c>
-      <c r="M149" t="n">
+      <c r="O149" t="n">
         <v>58607.94</v>
       </c>
     </row>
@@ -7559,20 +8461,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="J150" s="1" t="n">
+        <v>46196.92792824074</v>
+      </c>
+      <c r="K150" s="1" t="n">
+        <v>46196.92357638889</v>
+      </c>
+      <c r="L150" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L150" t="n">
+      <c r="N150" t="n">
         <v>58608</v>
       </c>
-      <c r="M150" t="n">
+      <c r="O150" t="n">
         <v>58607.94</v>
       </c>
     </row>
@@ -7612,20 +8520,26 @@
           <t>206</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="J151" s="1" t="n">
+        <v>46256.50920138889</v>
+      </c>
+      <c r="K151" s="1" t="n">
+        <v>46256.50922453704</v>
+      </c>
+      <c r="L151" t="inlineStr">
         <is>
           <t>Минск Алтайская ул. 206</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, Алтайская, 206</t>
         </is>
       </c>
-      <c r="L151" t="n">
+      <c r="N151" t="n">
         <v>83537</v>
       </c>
-      <c r="M151" t="n">
+      <c r="O151" t="n">
         <v>83536.95</v>
       </c>
     </row>
@@ -7665,20 +8579,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="J152" s="1" t="n">
+        <v>46225.62712962963</v>
+      </c>
+      <c r="K152" s="1" t="n">
+        <v>46225.64390046296</v>
+      </c>
+      <c r="L152" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22 А</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>Minsk, вуліца Жарэса Алфёрава, 22</t>
         </is>
       </c>
-      <c r="L152" t="n">
+      <c r="N152" t="n">
         <v>83207</v>
       </c>
-      <c r="M152" t="n">
+      <c r="O152" t="n">
         <v>83206.75999999999</v>
       </c>
     </row>
@@ -7710,20 +8630,26 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="J153" s="1" t="n">
+        <v>46255.30840277778</v>
+      </c>
+      <c r="K153" s="1" t="n">
+        <v>46255.31138888889</v>
+      </c>
+      <c r="L153" t="inlineStr">
         <is>
           <t>Минск Коласа пер. 5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t>Минск, переулок Якуба Коласа, 5</t>
         </is>
       </c>
-      <c r="L153" t="n">
+      <c r="N153" t="n">
         <v>77594</v>
       </c>
-      <c r="M153" t="n">
+      <c r="O153" t="n">
         <v>77593.61</v>
       </c>
     </row>
@@ -7755,20 +8681,26 @@
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr">
+      <c r="J154" s="1" t="n">
+        <v>46254.61443287037</v>
+      </c>
+      <c r="K154" s="1" t="n">
+        <v>46254.62070601852</v>
+      </c>
+      <c r="L154" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t>Минск</t>
         </is>
       </c>
-      <c r="L154" t="n">
+      <c r="N154" t="n">
         <v>75000</v>
       </c>
-      <c r="M154" t="n">
+      <c r="O154" t="n">
         <v>75000</v>
       </c>
     </row>
@@ -7800,20 +8732,26 @@
           <t>к6</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="J155" s="1" t="n">
+        <v>46164.59511574074</v>
+      </c>
+      <c r="K155" s="1" t="n">
+        <v>46164.60362268519</v>
+      </c>
+      <c r="L155" t="inlineStr">
         <is>
           <t>Минск Логойский тракт 21 6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t>Минск, Логойский тракт, 21 к6</t>
         </is>
       </c>
-      <c r="L155" t="n">
+      <c r="N155" t="n">
         <v>87500</v>
       </c>
-      <c r="M155" t="n">
+      <c r="O155" t="n">
         <v>87500</v>
       </c>
     </row>
@@ -7845,20 +8783,26 @@
           <t>85</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
+      <c r="J156" s="1" t="n">
+        <v>46188.58571759259</v>
+      </c>
+      <c r="K156" s="1" t="n">
+        <v>46188.67400462963</v>
+      </c>
+      <c r="L156" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 85</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 85</t>
         </is>
       </c>
-      <c r="L156" t="n">
+      <c r="N156" t="n">
         <v>86344</v>
       </c>
-      <c r="M156" t="n">
+      <c r="O156" t="n">
         <v>86343.53</v>
       </c>
     </row>
@@ -7898,20 +8842,26 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="J157" s="1" t="n">
+        <v>46254.38903935185</v>
+      </c>
+      <c r="K157" s="1" t="n">
+        <v>46254.38959490741</v>
+      </c>
+      <c r="L157" t="inlineStr">
         <is>
           <t>Минск Жореса Алфёрова ул. 22</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t>Минск, улица Жореса Алфёрова, 22</t>
         </is>
       </c>
-      <c r="L157" t="n">
+      <c r="N157" t="n">
         <v>80235</v>
       </c>
-      <c r="M157" t="n">
+      <c r="O157" t="n">
         <v>80235.09</v>
       </c>
     </row>
@@ -7943,20 +8893,26 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="J158" s="1" t="n">
+        <v>46194.38503472223</v>
+      </c>
+      <c r="K158" s="1" t="n">
+        <v>46194.47599537037</v>
+      </c>
+      <c r="L158" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 50</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t>Минск, Пушкина просп. 50</t>
         </is>
       </c>
-      <c r="L158" t="n">
+      <c r="N158" t="n">
         <v>101037</v>
       </c>
-      <c r="M158" t="n">
+      <c r="O158" t="n">
         <v>101036.78</v>
       </c>
     </row>
@@ -7996,20 +8952,26 @@
           <t>68</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="J159" s="1" t="n">
+        <v>46254.25549768518</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>46254.25711805555</v>
+      </c>
+      <c r="L159" t="inlineStr">
         <is>
           <t>Минск Седых ул. 68</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t>Минск, улица Седых, 68</t>
         </is>
       </c>
-      <c r="L159" t="n">
+      <c r="N159" t="n">
         <v>82546</v>
       </c>
-      <c r="M159" t="n">
+      <c r="O159" t="n">
         <v>82546.39</v>
       </c>
     </row>
@@ -8049,20 +9011,26 @@
           <t>66</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="J160" s="1" t="n">
+        <v>46253.49891203704</v>
+      </c>
+      <c r="K160" s="1" t="n">
+        <v>46253.49893518518</v>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t>Минск Якубова ул. 66 2</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Якубова, 66</t>
         </is>
       </c>
-      <c r="L160" t="n">
+      <c r="N160" t="n">
         <v>94763</v>
       </c>
-      <c r="M160" t="n">
+      <c r="O160" t="n">
         <v>94763.25999999999</v>
       </c>
     </row>
@@ -8102,20 +9070,26 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="J161" s="1" t="n">
+        <v>46253.35321759259</v>
+      </c>
+      <c r="K161" s="1" t="n">
+        <v>46253.35329861111</v>
+      </c>
+      <c r="L161" t="inlineStr">
         <is>
           <t>Минск Водолажского ул. 23</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, улица Водолажского, 23</t>
         </is>
       </c>
-      <c r="L161" t="n">
+      <c r="N161" t="n">
         <v>94103</v>
       </c>
-      <c r="M161" t="n">
+      <c r="O161" t="n">
         <v>94102.89</v>
       </c>
     </row>
@@ -8147,20 +9121,26 @@
           <t>38</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
+      <c r="J162" s="1" t="n">
+        <v>46252.583125</v>
+      </c>
+      <c r="K162" s="1" t="n">
+        <v>46252.58680555555</v>
+      </c>
+      <c r="L162" t="inlineStr">
         <is>
           <t>Минск Машерова просп. 38</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t>Минск, Машерова просп. 38</t>
         </is>
       </c>
-      <c r="L162" t="n">
+      <c r="N162" t="n">
         <v>117216</v>
       </c>
-      <c r="M162" t="n">
+      <c r="O162" t="n">
         <v>117215.88</v>
       </c>
     </row>
@@ -8200,20 +9180,26 @@
           <t>43</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="J163" s="1" t="n">
+        <v>46252.53197916667</v>
+      </c>
+      <c r="K163" s="1" t="n">
+        <v>46252.53383101852</v>
+      </c>
+      <c r="L163" t="inlineStr">
         <is>
           <t>Минск Калиновского ул. 43</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t>Минск, улица Калиновского, 43</t>
         </is>
       </c>
-      <c r="L163" t="n">
+      <c r="N163" t="n">
         <v>85001</v>
       </c>
-      <c r="M163" t="n">
+      <c r="O163" t="n">
         <v>85000.66</v>
       </c>
     </row>
@@ -8245,20 +9231,26 @@
           <t>16</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="J164" s="1" t="n">
+        <v>46252.38248842592</v>
+      </c>
+      <c r="K164" s="1" t="n">
+        <v>46252.37665509259</v>
+      </c>
+      <c r="L164" t="inlineStr">
         <is>
           <t>Минск Мира просп. 16</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t>Минская область, Минский район, Минск, Мира, 16</t>
         </is>
       </c>
-      <c r="L164" t="n">
+      <c r="N164" t="n">
         <v>97075</v>
       </c>
-      <c r="M164" t="n">
+      <c r="O164" t="n">
         <v>97074.56</v>
       </c>
     </row>
@@ -8290,20 +9282,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="J165" s="1" t="n">
+        <v>46252.36215277778</v>
+      </c>
+      <c r="K165" s="1" t="n">
+        <v>46260.20613425926</v>
+      </c>
+      <c r="L165" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 170</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t>Минск, Слободская улица, 15</t>
         </is>
       </c>
-      <c r="L165" t="n">
+      <c r="N165" t="n">
         <v>89480</v>
       </c>
-      <c r="M165" t="n">
+      <c r="O165" t="n">
         <v>85848.25</v>
       </c>
     </row>
@@ -8335,20 +9333,26 @@
           <t>28к1</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="J166" s="1" t="n">
+        <v>46252.36215277778</v>
+      </c>
+      <c r="K166" s="1" t="n">
+        <v>46220.62186342593</v>
+      </c>
+      <c r="L166" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 170</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>Минск, Звязда газеты просп. 28к1</t>
         </is>
       </c>
-      <c r="L166" t="n">
+      <c r="N166" t="n">
         <v>89480</v>
       </c>
-      <c r="M166" t="n">
+      <c r="O166" t="n">
         <v>80202.07000000001</v>
       </c>
     </row>
@@ -8380,20 +9384,26 @@
           <t>48</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="J167" s="1" t="n">
+        <v>46252.36215277778</v>
+      </c>
+      <c r="K167" s="1" t="n">
+        <v>46243.73265046296</v>
+      </c>
+      <c r="L167" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 170</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t>Минск, Космонавтов ул. 48</t>
         </is>
       </c>
-      <c r="L167" t="n">
+      <c r="N167" t="n">
         <v>89480</v>
       </c>
-      <c r="M167" t="n">
+      <c r="O167" t="n">
         <v>86838.8</v>
       </c>
     </row>
@@ -8425,20 +9435,26 @@
           <t>170</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
+      <c r="J168" s="1" t="n">
+        <v>46252.36215277778</v>
+      </c>
+      <c r="K168" s="1" t="n">
+        <v>46252.87851851852</v>
+      </c>
+      <c r="L168" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 170</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t>Минск, Рокоссовского просп. 170</t>
         </is>
       </c>
-      <c r="L168" t="n">
+      <c r="N168" t="n">
         <v>89480</v>
       </c>
-      <c r="M168" t="n">
+      <c r="O168" t="n">
         <v>89480.28999999999</v>
       </c>
     </row>
@@ -8478,20 +9494,26 @@
           <t>7</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="J169" s="1" t="n">
+        <v>46199.61716435185</v>
+      </c>
+      <c r="K169" s="1" t="n">
+        <v>46204.84662037037</v>
+      </c>
+      <c r="L169" t="inlineStr">
         <is>
           <t>Минск Дрозда ул. 7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>Минск, улица Дрозда, 7</t>
         </is>
       </c>
-      <c r="L169" t="n">
+      <c r="N169" t="n">
         <v>87500</v>
       </c>
-      <c r="M169" t="n">
+      <c r="O169" t="n">
         <v>89000</v>
       </c>
     </row>
@@ -8523,20 +9545,26 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="J170" s="1" t="n">
+        <v>46244.52864583334</v>
+      </c>
+      <c r="K170" s="1" t="n">
+        <v>46262.50825231482</v>
+      </c>
+      <c r="L170" t="inlineStr">
         <is>
           <t>Минск Козлова пер. 12</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t>Минск, переулок Козлова, 12</t>
         </is>
       </c>
-      <c r="L170" t="n">
+      <c r="N170" t="n">
         <v>77000</v>
       </c>
-      <c r="M170" t="n">
+      <c r="O170" t="n">
         <v>77000</v>
       </c>
     </row>
@@ -8568,20 +9596,26 @@
           <t>26</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="J171" s="1" t="n">
+        <v>46244.44158564815</v>
+      </c>
+      <c r="K171" s="1" t="n">
+        <v>46244.4371875</v>
+      </c>
+      <c r="L171" t="inlineStr">
         <is>
           <t>Минск Пушкина просп. 26</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t>Минск, проспект Пушкина, 26</t>
         </is>
       </c>
-      <c r="L171" t="n">
+      <c r="N171" t="n">
         <v>110000</v>
       </c>
-      <c r="M171" t="n">
+      <c r="O171" t="n">
         <v>110000</v>
       </c>
     </row>
@@ -8621,20 +9655,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="J172" s="1" t="n">
+        <v>46224.53203703704</v>
+      </c>
+      <c r="K172" s="1" t="n">
+        <v>46224.54065972222</v>
+      </c>
+      <c r="L172" t="inlineStr">
         <is>
           <t>Минск Скрипникова ул. 15</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t>Минск, улица Скрипникова, 15</t>
         </is>
       </c>
-      <c r="L172" t="n">
+      <c r="N172" t="n">
         <v>115000</v>
       </c>
-      <c r="M172" t="n">
+      <c r="O172" t="n">
         <v>115000</v>
       </c>
     </row>
@@ -8674,20 +9714,26 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="J173" s="1" t="n">
+        <v>46225.51892361111</v>
+      </c>
+      <c r="K173" s="1" t="n">
+        <v>46225.57253472223</v>
+      </c>
+      <c r="L173" t="inlineStr">
         <is>
           <t>Минск Куйбышева ул. 30</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t>Минск, улица Куйбышева, 30</t>
         </is>
       </c>
-      <c r="L173" t="n">
+      <c r="N173" t="n">
         <v>120000</v>
       </c>
-      <c r="M173" t="n">
+      <c r="O173" t="n">
         <v>120000</v>
       </c>
     </row>
@@ -8719,20 +9765,26 @@
           <t>109</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="J174" s="1" t="n">
+        <v>46218.57744212963</v>
+      </c>
+      <c r="K174" s="1" t="n">
+        <v>46218.61489583334</v>
+      </c>
+      <c r="L174" t="inlineStr">
         <is>
           <t>Минск Рокоссовского просп. 109</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t>Минск, проспект Рокоссовского, 109</t>
         </is>
       </c>
-      <c r="L174" t="n">
+      <c r="N174" t="n">
         <v>85000</v>
       </c>
-      <c r="M174" t="n">
+      <c r="O174" t="n">
         <v>85000</v>
       </c>
     </row>
@@ -8772,20 +9824,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="J175" s="1" t="n">
+        <v>46203.35177083333</v>
+      </c>
+      <c r="K175" s="1" t="n">
+        <v>46259.42888888889</v>
+      </c>
+      <c r="L175" t="inlineStr">
         <is>
           <t>Минск Щорса ул. 1</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t>Minsk, вуліца Шчорса, 1</t>
         </is>
       </c>
-      <c r="L175" t="n">
+      <c r="N175" t="n">
         <v>97000</v>
       </c>
-      <c r="M175" t="n">
+      <c r="O175" t="n">
         <v>115102.69</v>
       </c>
     </row>
@@ -8825,20 +9883,26 @@
           <t>37</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="J176" s="1" t="n">
+        <v>46179.53146990741</v>
+      </c>
+      <c r="K176" s="1" t="n">
+        <v>46263.65082175926</v>
+      </c>
+      <c r="L176" t="inlineStr">
         <is>
           <t>Минск Выготского ул. 37</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t>Минск, улица Выготского, 37</t>
         </is>
       </c>
-      <c r="L176" t="n">
+      <c r="N176" t="n">
         <v>81000</v>
       </c>
-      <c r="M176" t="n">
+      <c r="O176" t="n">
         <v>80500</v>
       </c>
     </row>
@@ -8870,20 +9934,26 @@
           <t>30к1</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="J177" s="1" t="n">
+        <v>46178.55856481481</v>
+      </c>
+      <c r="K177" s="1" t="n">
+        <v>46189.88907407408</v>
+      </c>
+      <c r="L177" t="inlineStr">
         <is>
           <t>Минск Чайковского проезд 6</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t>Минск, Семенова ул. 30к1</t>
         </is>
       </c>
-      <c r="L177" t="n">
+      <c r="N177" t="n">
         <v>92000</v>
       </c>
-      <c r="M177" t="n">
+      <c r="O177" t="n">
         <v>102000</v>
       </c>
     </row>
@@ -8915,20 +9985,26 @@
           <t>19</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="J178" s="1" t="n">
+        <v>46178.55856481481</v>
+      </c>
+      <c r="K178" s="1" t="n">
+        <v>46258.49653935185</v>
+      </c>
+      <c r="L178" t="inlineStr">
         <is>
           <t>Минск Чайковского проезд 6</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t>Минск, Волгоградская ул. 19</t>
         </is>
       </c>
-      <c r="L178" t="n">
+      <c r="N178" t="n">
         <v>92000</v>
       </c>
-      <c r="M178" t="n">
+      <c r="O178" t="n">
         <v>91128.89999999999</v>
       </c>
     </row>
@@ -8960,20 +10036,26 @@
           <t>24</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="J179" s="1" t="n">
+        <v>46047.43420138889</v>
+      </c>
+      <c r="K179" s="1" t="n">
+        <v>46252.87854166667</v>
+      </c>
+      <c r="L179" t="inlineStr">
         <is>
           <t>Минск Аэродромная ул.</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t>Минск, Савицкого ул. 24</t>
         </is>
       </c>
-      <c r="L179" t="n">
+      <c r="N179" t="n">
         <v>61000</v>
       </c>
-      <c r="M179" t="n">
+      <c r="O179" t="n">
         <v>80235.09</v>
       </c>
     </row>
@@ -9013,20 +10095,26 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="J180" s="1" t="n">
+        <v>46156.79502314814</v>
+      </c>
+      <c r="K180" s="1" t="n">
+        <v>46156.77068287037</v>
+      </c>
+      <c r="L180" t="inlineStr">
         <is>
           <t>Минск Белинского ул. 15</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>Минск, улица Белинского, 15</t>
         </is>
       </c>
-      <c r="L180" t="n">
+      <c r="N180" t="n">
         <v>100999</v>
       </c>
-      <c r="M180" t="n">
+      <c r="O180" t="n">
         <v>100999</v>
       </c>
     </row>
@@ -9066,20 +10154,26 @@
           <t>51</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="J181" s="1" t="n">
+        <v>46149.59554398148</v>
+      </c>
+      <c r="K181" s="1" t="n">
+        <v>46150.34540509259</v>
+      </c>
+      <c r="L181" t="inlineStr">
         <is>
           <t>Минск Мирошниченко ул. 51</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t>Минск, улица Мирошниченко, 51</t>
         </is>
       </c>
-      <c r="L181" t="n">
+      <c r="N181" t="n">
         <v>94900</v>
       </c>
-      <c r="M181" t="n">
+      <c r="O181" t="n">
         <v>95000</v>
       </c>
     </row>
@@ -9111,20 +10205,26 @@
           <t>24</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="J182" s="1" t="n">
+        <v>46148.39155092592</v>
+      </c>
+      <c r="K182" s="1" t="n">
+        <v>46272.64703703704</v>
+      </c>
+      <c r="L182" t="inlineStr">
         <is>
           <t>Минск Радужная ул.</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t>Минск, улица Герасименко, 24</t>
         </is>
       </c>
-      <c r="L182" t="n">
+      <c r="N182" t="n">
         <v>72641</v>
       </c>
-      <c r="M182" t="n">
+      <c r="O182" t="n">
         <v>76500</v>
       </c>
     </row>
@@ -9164,20 +10264,26 @@
           <t>45</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
+      <c r="J183" s="1" t="n">
+        <v>46147.76222222222</v>
+      </c>
+      <c r="K183" s="1" t="n">
+        <v>46147.75565972222</v>
+      </c>
+      <c r="L183" t="inlineStr">
         <is>
           <t>Минск Мирошниченко ул. 45</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t>Минск, улица Мирошниченко, 45</t>
         </is>
       </c>
-      <c r="L183" t="n">
+      <c r="N183" t="n">
         <v>115000</v>
       </c>
-      <c r="M183" t="n">
+      <c r="O183" t="n">
         <v>115000</v>
       </c>
     </row>
@@ -9209,20 +10315,26 @@
           <t>24</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="J184" s="1" t="n">
+        <v>46124.34487268519</v>
+      </c>
+      <c r="K184" s="1" t="n">
+        <v>46272.64703703704</v>
+      </c>
+      <c r="L184" t="inlineStr">
         <is>
           <t>Минск Независимости просп. 151 1</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t>Минск, улица Герасименко, 24</t>
         </is>
       </c>
-      <c r="L184" t="n">
+      <c r="N184" t="n">
         <v>87500</v>
       </c>
-      <c r="M184" t="n">
+      <c r="O184" t="n">
         <v>76500</v>
       </c>
     </row>
@@ -9246,20 +10358,26 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr">
+      <c r="J185" s="1" t="n">
+        <v>46071.70850694444</v>
+      </c>
+      <c r="K185" s="1" t="n">
+        <v>46094.71254629629</v>
+      </c>
+      <c r="L185" t="inlineStr">
         <is>
           <t>Минск Корженевского пер. 18</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t>Минск, переулок Корженевского</t>
         </is>
       </c>
-      <c r="L185" t="n">
+      <c r="N185" t="n">
         <v>97000</v>
       </c>
-      <c r="M185" t="n">
+      <c r="O185" t="n">
         <v>97000</v>
       </c>
     </row>
